--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.13710625591763</v>
+        <v>7.497279766586615</v>
       </c>
       <c r="D2" t="n">
-        <v>47.96970197615153</v>
+        <v>7.795076571124623</v>
       </c>
       <c r="E2" t="n">
-        <v>21.60684981487635</v>
+        <v>3.511113094917407</v>
       </c>
       <c r="F2" t="n">
-        <v>21.42014149239642</v>
+        <v>3.480772992514418</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.61446277316941</v>
+        <v>8.54985020064003</v>
       </c>
       <c r="D3" t="n">
-        <v>50.82454519635669</v>
+        <v>8.258988594407962</v>
       </c>
       <c r="E3" t="n">
-        <v>21.60684981487635</v>
+        <v>3.511113094917407</v>
       </c>
       <c r="F3" t="n">
-        <v>21.42014149239642</v>
+        <v>3.480772992514418</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.87501204201285</v>
+        <v>2.417189456827089</v>
       </c>
       <c r="D4" t="n">
-        <v>12.75569349473224</v>
+        <v>2.072800192893989</v>
       </c>
       <c r="E4" t="n">
-        <v>21.60684981487635</v>
+        <v>3.511113094917407</v>
       </c>
       <c r="F4" t="n">
-        <v>21.42014149239642</v>
+        <v>3.480772992514418</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>75.48499963932038</v>
+        <v>12.26631244138956</v>
       </c>
       <c r="D5" t="n">
-        <v>73.38614170057578</v>
+        <v>11.92524802634356</v>
       </c>
       <c r="E5" t="n">
-        <v>21.60684981487635</v>
+        <v>3.511113094917407</v>
       </c>
       <c r="F5" t="n">
-        <v>21.42014149239642</v>
+        <v>3.480772992514418</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.75314313128599</v>
+        <v>6.297385758833974</v>
       </c>
       <c r="D6" t="n">
-        <v>36.57808428952274</v>
+        <v>5.943938697047446</v>
       </c>
       <c r="E6" t="n">
-        <v>21.60684981487635</v>
+        <v>3.511113094917407</v>
       </c>
       <c r="F6" t="n">
-        <v>21.42014149239642</v>
+        <v>3.480772992514418</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>77.23857326240372</v>
+        <v>12.5512681551406</v>
       </c>
       <c r="D7" t="n">
-        <v>75.04670435991768</v>
+        <v>12.19508945848662</v>
       </c>
       <c r="E7" t="n">
-        <v>21.60684981487635</v>
+        <v>3.511113094917407</v>
       </c>
       <c r="F7" t="n">
-        <v>21.42014149239642</v>
+        <v>3.480772992514418</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>74.97610011730882</v>
+        <v>12.18361626906268</v>
       </c>
       <c r="D8" t="n">
-        <v>72.77825404402964</v>
+        <v>11.82646628215482</v>
       </c>
       <c r="E8" t="n">
-        <v>21.60684981487635</v>
+        <v>3.511113094917407</v>
       </c>
       <c r="F8" t="n">
-        <v>21.42014149239642</v>
+        <v>3.480772992514418</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
